--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123803294</v>
+        <v>123801256</v>
       </c>
       <c r="B2" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588123</v>
+        <v>588155</v>
       </c>
       <c r="R2" t="n">
-        <v>6388420</v>
+        <v>6388343</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801256</v>
+        <v>123803294</v>
       </c>
       <c r="B3" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588155</v>
+        <v>588123</v>
       </c>
       <c r="R3" t="n">
-        <v>6388343</v>
+        <v>6388420</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123801289</v>
+        <v>123803106</v>
       </c>
       <c r="B4" t="n">
-        <v>95167</v>
+        <v>95173</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588174</v>
+        <v>588158</v>
       </c>
       <c r="R4" t="n">
-        <v>6388368</v>
+        <v>6388440</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123801172</v>
+        <v>123801461</v>
       </c>
       <c r="B5" t="n">
-        <v>57493</v>
+        <v>58168</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,20 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100048</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,21 +1045,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588155</v>
+        <v>588185</v>
       </c>
       <c r="R5" t="n">
-        <v>6388343</v>
+        <v>6388361</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123803363</v>
+        <v>123802891</v>
       </c>
       <c r="B6" t="n">
-        <v>95167</v>
+        <v>57643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,41 +1135,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588124</v>
+        <v>588167</v>
       </c>
       <c r="R6" t="n">
-        <v>6388406</v>
+        <v>6388438</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123802891</v>
+        <v>123801172</v>
       </c>
       <c r="B7" t="n">
-        <v>57640</v>
+        <v>57496</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588167</v>
+        <v>588155</v>
       </c>
       <c r="R7" t="n">
-        <v>6388438</v>
+        <v>6388343</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123801461</v>
+        <v>123803363</v>
       </c>
       <c r="B8" t="n">
-        <v>58165</v>
+        <v>95173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,37 +1373,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588185</v>
+        <v>588124</v>
       </c>
       <c r="R8" t="n">
-        <v>6388361</v>
+        <v>6388406</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1472,7 +1472,7 @@
         <v>123802264</v>
       </c>
       <c r="B9" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123803214</v>
+        <v>123801289</v>
       </c>
       <c r="B10" t="n">
-        <v>57503</v>
+        <v>95173</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,46 +1598,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588122</v>
+        <v>588174</v>
       </c>
       <c r="R10" t="n">
-        <v>6388440</v>
+        <v>6388368</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123803106</v>
+        <v>123803214</v>
       </c>
       <c r="B11" t="n">
-        <v>95167</v>
+        <v>57506</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,41 +1710,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588158</v>
+        <v>588122</v>
       </c>
       <c r="R11" t="n">
         <v>6388440</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123801256</v>
+        <v>123803363</v>
       </c>
       <c r="B2" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588155</v>
+        <v>588124</v>
       </c>
       <c r="R2" t="n">
-        <v>6388343</v>
+        <v>6388406</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123803294</v>
+        <v>123803214</v>
       </c>
       <c r="B3" t="n">
-        <v>95173</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588123</v>
+        <v>588122</v>
       </c>
       <c r="R3" t="n">
-        <v>6388420</v>
+        <v>6388440</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123803106</v>
+        <v>123802264</v>
       </c>
       <c r="B4" t="n">
-        <v>95173</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588158</v>
+        <v>588168</v>
       </c>
       <c r="R4" t="n">
-        <v>6388440</v>
+        <v>6388437</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1024,7 @@
         <v>123801461</v>
       </c>
       <c r="B5" t="n">
-        <v>58168</v>
+        <v>58169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802891</v>
+        <v>123801256</v>
       </c>
       <c r="B6" t="n">
-        <v>57643</v>
+        <v>95175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,46 +1145,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588167</v>
+        <v>588155</v>
       </c>
       <c r="R6" t="n">
-        <v>6388438</v>
+        <v>6388343</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123801172</v>
+        <v>123803294</v>
       </c>
       <c r="B7" t="n">
-        <v>57496</v>
+        <v>95175</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,46 +1257,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588155</v>
+        <v>588123</v>
       </c>
       <c r="R7" t="n">
-        <v>6388343</v>
+        <v>6388420</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123803363</v>
+        <v>123803106</v>
       </c>
       <c r="B8" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588124</v>
+        <v>588158</v>
       </c>
       <c r="R8" t="n">
-        <v>6388406</v>
+        <v>6388440</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123802264</v>
+        <v>123801289</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>95175</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,43 +1481,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588168</v>
+        <v>588174</v>
       </c>
       <c r="R9" t="n">
-        <v>6388437</v>
+        <v>6388368</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123801289</v>
+        <v>123802891</v>
       </c>
       <c r="B10" t="n">
-        <v>95173</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,41 +1593,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588174</v>
+        <v>588167</v>
       </c>
       <c r="R10" t="n">
-        <v>6388368</v>
+        <v>6388438</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123803214</v>
+        <v>123801172</v>
       </c>
       <c r="B11" t="n">
-        <v>57506</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,16 +1714,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1734,19 +1734,19 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588122</v>
+        <v>588155</v>
       </c>
       <c r="R11" t="n">
-        <v>6388440</v>
+        <v>6388343</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123803363</v>
+        <v>123801172</v>
       </c>
       <c r="B2" t="n">
-        <v>95175</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588124</v>
+        <v>588155</v>
       </c>
       <c r="R2" t="n">
-        <v>6388406</v>
+        <v>6388343</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123803214</v>
+        <v>123803294</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,46 +804,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588122</v>
+        <v>588123</v>
       </c>
       <c r="R3" t="n">
-        <v>6388440</v>
+        <v>6388420</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802264</v>
+        <v>123801461</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>58169</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,20 +916,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,24 +938,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588168</v>
+        <v>588185</v>
       </c>
       <c r="R4" t="n">
-        <v>6388437</v>
+        <v>6388361</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123801461</v>
+        <v>123801256</v>
       </c>
       <c r="B5" t="n">
-        <v>58169</v>
+        <v>95683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588185</v>
+        <v>588155</v>
       </c>
       <c r="R5" t="n">
-        <v>6388361</v>
+        <v>6388343</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123801256</v>
+        <v>123803214</v>
       </c>
       <c r="B6" t="n">
-        <v>95175</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,41 +1140,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588155</v>
+        <v>588122</v>
       </c>
       <c r="R6" t="n">
-        <v>6388343</v>
+        <v>6388440</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123803294</v>
+        <v>123803363</v>
       </c>
       <c r="B7" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588123</v>
+        <v>588124</v>
       </c>
       <c r="R7" t="n">
-        <v>6388420</v>
+        <v>6388406</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123803106</v>
+        <v>123801289</v>
       </c>
       <c r="B8" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,14 +1393,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588158</v>
+        <v>588174</v>
       </c>
       <c r="R8" t="n">
-        <v>6388440</v>
+        <v>6388368</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123801289</v>
+        <v>123802264</v>
       </c>
       <c r="B9" t="n">
-        <v>95175</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,38 +1481,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588174</v>
+        <v>588168</v>
       </c>
       <c r="R9" t="n">
-        <v>6388368</v>
+        <v>6388437</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123802891</v>
+        <v>123803106</v>
       </c>
       <c r="B10" t="n">
-        <v>57644</v>
+        <v>95683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,46 +1598,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588167</v>
+        <v>588158</v>
       </c>
       <c r="R10" t="n">
-        <v>6388438</v>
+        <v>6388440</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123801172</v>
+        <v>123802891</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588155</v>
+        <v>588167</v>
       </c>
       <c r="R11" t="n">
-        <v>6388343</v>
+        <v>6388438</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123801172</v>
+        <v>123803294</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>95683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588155</v>
+        <v>588123</v>
       </c>
       <c r="R2" t="n">
-        <v>6388343</v>
+        <v>6388420</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123803294</v>
+        <v>123801172</v>
       </c>
       <c r="B3" t="n">
-        <v>95683</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,41 +799,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588123</v>
+        <v>588155</v>
       </c>
       <c r="R3" t="n">
-        <v>6388420</v>
+        <v>6388343</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123803294</v>
+        <v>123803106</v>
       </c>
       <c r="B2" t="n">
         <v>95683</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588123</v>
+        <v>588158</v>
       </c>
       <c r="R2" t="n">
-        <v>6388420</v>
+        <v>6388440</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123801461</v>
+        <v>123801256</v>
       </c>
       <c r="B4" t="n">
-        <v>58169</v>
+        <v>95683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588185</v>
+        <v>588155</v>
       </c>
       <c r="R4" t="n">
-        <v>6388361</v>
+        <v>6388343</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123801256</v>
+        <v>123802891</v>
       </c>
       <c r="B5" t="n">
-        <v>95683</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1028,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588155</v>
+        <v>588167</v>
       </c>
       <c r="R5" t="n">
-        <v>6388343</v>
+        <v>6388438</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123803214</v>
+        <v>123801289</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,46 +1145,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588122</v>
+        <v>588174</v>
       </c>
       <c r="R6" t="n">
-        <v>6388440</v>
+        <v>6388368</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123801289</v>
+        <v>123801461</v>
       </c>
       <c r="B8" t="n">
-        <v>95683</v>
+        <v>58169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588174</v>
+        <v>588185</v>
       </c>
       <c r="R8" t="n">
-        <v>6388368</v>
+        <v>6388361</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1469,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123802264</v>
+        <v>123803214</v>
       </c>
       <c r="B9" t="n">
         <v>57507</v>
@@ -1514,13 +1514,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588168</v>
+        <v>588122</v>
       </c>
       <c r="R9" t="n">
-        <v>6388437</v>
+        <v>6388440</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123803106</v>
+        <v>123802264</v>
       </c>
       <c r="B10" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,38 +1598,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588158</v>
+        <v>588168</v>
       </c>
       <c r="R10" t="n">
-        <v>6388440</v>
+        <v>6388437</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123802891</v>
+        <v>123803294</v>
       </c>
       <c r="B11" t="n">
-        <v>57644</v>
+        <v>95683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,46 +1715,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588167</v>
+        <v>588123</v>
       </c>
       <c r="R11" t="n">
-        <v>6388438</v>
+        <v>6388420</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123803106</v>
+        <v>123803294</v>
       </c>
       <c r="B2" t="n">
         <v>95683</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588158</v>
+        <v>588123</v>
       </c>
       <c r="R2" t="n">
-        <v>6388440</v>
+        <v>6388420</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801172</v>
+        <v>123801256</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,33 +799,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kristofferslund, Kristofferslund, Sm</t>
@@ -838,7 +833,7 @@
         <v>6388343</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123801256</v>
+        <v>123802264</v>
       </c>
       <c r="B4" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588155</v>
+        <v>588168</v>
       </c>
       <c r="R4" t="n">
-        <v>6388343</v>
+        <v>6388437</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802891</v>
+        <v>123803106</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>95683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,46 +1028,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588167</v>
+        <v>588158</v>
       </c>
       <c r="R5" t="n">
-        <v>6388438</v>
+        <v>6388440</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123801289</v>
+        <v>123801461</v>
       </c>
       <c r="B6" t="n">
-        <v>95683</v>
+        <v>58169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588174</v>
+        <v>588185</v>
       </c>
       <c r="R6" t="n">
-        <v>6388368</v>
+        <v>6388361</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123803363</v>
+        <v>123801289</v>
       </c>
       <c r="B7" t="n">
         <v>95683</v>
@@ -1281,14 +1276,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588124</v>
+        <v>588174</v>
       </c>
       <c r="R7" t="n">
-        <v>6388406</v>
+        <v>6388368</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123801461</v>
+        <v>123803363</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>95683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,37 +1368,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588185</v>
+        <v>588124</v>
       </c>
       <c r="R8" t="n">
-        <v>6388361</v>
+        <v>6388406</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123802264</v>
+        <v>123802891</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,27 +1597,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1631,13 +1626,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588168</v>
+        <v>588167</v>
       </c>
       <c r="R10" t="n">
-        <v>6388437</v>
+        <v>6388438</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123803294</v>
+        <v>123801172</v>
       </c>
       <c r="B11" t="n">
-        <v>95683</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,41 +1710,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2180</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588123</v>
+        <v>588155</v>
       </c>
       <c r="R11" t="n">
-        <v>6388420</v>
+        <v>6388343</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123803294</v>
+        <v>123801256</v>
       </c>
       <c r="B2" t="n">
         <v>95683</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588123</v>
+        <v>588155</v>
       </c>
       <c r="R2" t="n">
-        <v>6388420</v>
+        <v>6388343</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801256</v>
+        <v>123801461</v>
       </c>
       <c r="B3" t="n">
-        <v>95683</v>
+        <v>58169</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588155</v>
+        <v>588185</v>
       </c>
       <c r="R3" t="n">
-        <v>6388343</v>
+        <v>6388361</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,7 +1016,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123803106</v>
+        <v>123801289</v>
       </c>
       <c r="B5" t="n">
         <v>95683</v>
@@ -1052,14 +1052,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588158</v>
+        <v>588174</v>
       </c>
       <c r="R5" t="n">
-        <v>6388440</v>
+        <v>6388368</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123801461</v>
+        <v>123803106</v>
       </c>
       <c r="B6" t="n">
-        <v>58169</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,37 +1144,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588185</v>
+        <v>588158</v>
       </c>
       <c r="R6" t="n">
-        <v>6388361</v>
+        <v>6388440</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123801289</v>
+        <v>123803294</v>
       </c>
       <c r="B7" t="n">
         <v>95683</v>
@@ -1276,14 +1276,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588174</v>
+        <v>588123</v>
       </c>
       <c r="R7" t="n">
-        <v>6388368</v>
+        <v>6388420</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123803363</v>
+        <v>123801172</v>
       </c>
       <c r="B8" t="n">
-        <v>95683</v>
+        <v>57497</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,41 +1364,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2180</v>
+        <v>100048</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588124</v>
+        <v>588155</v>
       </c>
       <c r="R8" t="n">
-        <v>6388406</v>
+        <v>6388343</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123803214</v>
+        <v>123803363</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,46 +1481,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588122</v>
+        <v>588124</v>
       </c>
       <c r="R9" t="n">
-        <v>6388440</v>
+        <v>6388406</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123802891</v>
+        <v>123803214</v>
       </c>
       <c r="B10" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,27 +1597,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588167</v>
+        <v>588122</v>
       </c>
       <c r="R10" t="n">
-        <v>6388438</v>
+        <v>6388440</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123801172</v>
+        <v>123802891</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588155</v>
+        <v>588167</v>
       </c>
       <c r="R11" t="n">
-        <v>6388343</v>
+        <v>6388438</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123801256</v>
+        <v>123801461</v>
       </c>
       <c r="B2" t="n">
-        <v>95683</v>
+        <v>58169</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588155</v>
+        <v>588185</v>
       </c>
       <c r="R2" t="n">
-        <v>6388343</v>
+        <v>6388361</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801461</v>
+        <v>123801172</v>
       </c>
       <c r="B3" t="n">
-        <v>58169</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,16 +821,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588185</v>
+        <v>588155</v>
       </c>
       <c r="R3" t="n">
-        <v>6388361</v>
+        <v>6388343</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802264</v>
+        <v>123803214</v>
       </c>
       <c r="B4" t="n">
         <v>57507</v>
@@ -944,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588168</v>
+        <v>588122</v>
       </c>
       <c r="R4" t="n">
-        <v>6388437</v>
+        <v>6388440</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123801289</v>
+        <v>123802891</v>
       </c>
       <c r="B5" t="n">
-        <v>95683</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1033,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588174</v>
+        <v>588167</v>
       </c>
       <c r="R5" t="n">
-        <v>6388368</v>
+        <v>6388438</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123803106</v>
+        <v>123802264</v>
       </c>
       <c r="B6" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1150,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588158</v>
+        <v>588168</v>
       </c>
       <c r="R6" t="n">
-        <v>6388440</v>
+        <v>6388437</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1203,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123803294</v>
+        <v>123803363</v>
       </c>
       <c r="B7" t="n">
         <v>95683</v>
@@ -1280,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588123</v>
+        <v>588124</v>
       </c>
       <c r="R7" t="n">
-        <v>6388420</v>
+        <v>6388406</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1315,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123801172</v>
+        <v>123803294</v>
       </c>
       <c r="B8" t="n">
-        <v>57497</v>
+        <v>95683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,46 +1379,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588155</v>
+        <v>588123</v>
       </c>
       <c r="R8" t="n">
-        <v>6388343</v>
+        <v>6388420</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123803363</v>
+        <v>123803106</v>
       </c>
       <c r="B9" t="n">
         <v>95683</v>
@@ -1509,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588124</v>
+        <v>588158</v>
       </c>
       <c r="R9" t="n">
-        <v>6388406</v>
+        <v>6388440</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123803214</v>
+        <v>123801289</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,46 +1603,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588122</v>
+        <v>588174</v>
       </c>
       <c r="R10" t="n">
-        <v>6388440</v>
+        <v>6388368</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123802891</v>
+        <v>123801256</v>
       </c>
       <c r="B11" t="n">
-        <v>57644</v>
+        <v>95683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,46 +1715,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588167</v>
+        <v>588155</v>
       </c>
       <c r="R11" t="n">
-        <v>6388438</v>
+        <v>6388343</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123801256</v>
+        <v>123803363</v>
       </c>
       <c r="B2" t="n">
         <v>95705</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588155</v>
+        <v>588124</v>
       </c>
       <c r="R2" t="n">
-        <v>6388343</v>
+        <v>6388406</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123802264</v>
+        <v>123801289</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>95705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588168</v>
+        <v>588174</v>
       </c>
       <c r="R3" t="n">
-        <v>6388437</v>
+        <v>6388368</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123803214</v>
+        <v>123802891</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,27 +915,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588122</v>
+        <v>588167</v>
       </c>
       <c r="R4" t="n">
-        <v>6388440</v>
+        <v>6388438</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802891</v>
+        <v>123802264</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,27 +1032,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588167</v>
+        <v>588168</v>
       </c>
       <c r="R5" t="n">
-        <v>6388438</v>
+        <v>6388437</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1133,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123803363</v>
+        <v>123801256</v>
       </c>
       <c r="B6" t="n">
         <v>95705</v>
@@ -1174,14 +1169,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588124</v>
+        <v>588155</v>
       </c>
       <c r="R6" t="n">
-        <v>6388406</v>
+        <v>6388343</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123801289</v>
+        <v>123803294</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1286,14 +1281,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588174</v>
+        <v>588123</v>
       </c>
       <c r="R7" t="n">
-        <v>6388368</v>
+        <v>6388420</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1325,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123801172</v>
+        <v>123803214</v>
       </c>
       <c r="B8" t="n">
-        <v>57519</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,16 +1373,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1398,19 +1393,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588155</v>
+        <v>588122</v>
       </c>
       <c r="R8" t="n">
-        <v>6388343</v>
+        <v>6388440</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1591,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123803106</v>
+        <v>123801172</v>
       </c>
       <c r="B10" t="n">
-        <v>95705</v>
+        <v>57519</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,41 +1598,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588158</v>
+        <v>588155</v>
       </c>
       <c r="R10" t="n">
-        <v>6388440</v>
+        <v>6388343</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123803294</v>
+        <v>123803106</v>
       </c>
       <c r="B11" t="n">
         <v>95705</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588123</v>
+        <v>588158</v>
       </c>
       <c r="R11" t="n">
-        <v>6388420</v>
+        <v>6388440</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12335-2025 artfynd.xlsx
+++ b/artfynd/A 12335-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123803363</v>
+        <v>123801461</v>
       </c>
       <c r="B2" t="n">
-        <v>95705</v>
+        <v>58191</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>103044</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588124</v>
+        <v>588185</v>
       </c>
       <c r="R2" t="n">
-        <v>6388406</v>
+        <v>6388361</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801289</v>
+        <v>123802264</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588174</v>
+        <v>588168</v>
       </c>
       <c r="R3" t="n">
-        <v>6388368</v>
+        <v>6388437</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802891</v>
+        <v>123801172</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57519</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ålhusmossen, Ålhusmossen, Sm</t>
+          <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588167</v>
+        <v>588155</v>
       </c>
       <c r="R4" t="n">
-        <v>6388438</v>
+        <v>6388343</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802264</v>
+        <v>123803214</v>
       </c>
       <c r="B5" t="n">
         <v>57529</v>
@@ -1061,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588168</v>
+        <v>588122</v>
       </c>
       <c r="R5" t="n">
-        <v>6388437</v>
+        <v>6388440</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,7 +1138,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123801256</v>
+        <v>123803106</v>
       </c>
       <c r="B6" t="n">
         <v>95705</v>
@@ -1169,14 +1174,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kristofferslund, Kristofferslund, Sm</t>
+          <t>Ålhusmossen, Ålhusmossen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588155</v>
+        <v>588158</v>
       </c>
       <c r="R6" t="n">
-        <v>6388343</v>
+        <v>6388440</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123803294</v>
+        <v>123803363</v>
       </c>
       <c r="B7" t="n">
         <v>95705</v>
@@ -1285,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588123</v>
+        <v>588124</v>
       </c>
       <c r="R7" t="n">
-        <v>6388420</v>
+        <v>6388406</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123803214</v>
+        <v>123802891</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,27 +1378,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>588122</v>
+        <v>588167</v>
       </c>
       <c r="R8" t="n">
-        <v>6388440</v>
+        <v>6388438</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123801461</v>
+        <v>123801256</v>
       </c>
       <c r="B9" t="n">
-        <v>58191</v>
+        <v>95705</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103044</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,13 +1519,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>588185</v>
+        <v>588155</v>
       </c>
       <c r="R9" t="n">
-        <v>6388361</v>
+        <v>6388343</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1549,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123801172</v>
+        <v>123801289</v>
       </c>
       <c r="B10" t="n">
-        <v>57519</v>
+        <v>95705</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,46 +1603,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kristofferslund, Kristofferslund, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>588155</v>
+        <v>588174</v>
       </c>
       <c r="R10" t="n">
-        <v>6388343</v>
+        <v>6388368</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123803106</v>
+        <v>123803294</v>
       </c>
       <c r="B11" t="n">
         <v>95705</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>588158</v>
+        <v>588123</v>
       </c>
       <c r="R11" t="n">
-        <v>6388440</v>
+        <v>6388420</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
